--- a/artfynd/A 2389-2024 artfynd.xlsx
+++ b/artfynd/A 2389-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2389-2024 artfynd.xlsx
+++ b/artfynd/A 2389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108693026</v>
+        <v>108693025</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443518.563544584</v>
+        <v>443518</v>
       </c>
       <c r="R2" t="n">
-        <v>6438266.193202948</v>
+        <v>6438266</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,19 +755,9 @@
           <t>2023-05-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,49 +785,36 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108693025</v>
+        <v>108693024</v>
       </c>
       <c r="B3" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443518.563544584</v>
+        <v>443518</v>
       </c>
       <c r="R3" t="n">
-        <v>6438266.193202948</v>
+        <v>6438266</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -881,19 +857,14 @@
           <t>2023-05-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,6 +889,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108693026</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brunnsmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>443518</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6438266</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Daretorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2389-2024 artfynd.xlsx
+++ b/artfynd/A 2389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108693025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108693024</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,8 +1010,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108693026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>